--- a/data/incidents_full_report.xlsx
+++ b/data/incidents_full_report.xlsx
@@ -1,20 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -93,7 +88,7 @@
     <t>Created_At</t>
   </si>
   <si>
-    <t>74ff597804244c7ca09f2d3f8c785868</t>
+    <t>ba90ac0c9fef442791e165f9ac4cfea0</t>
   </si>
   <si>
     <t>2018-06-16</t>
@@ -120,7 +115,7 @@
     <t>NA</t>
   </si>
   <si>
-    <t xml:space="preserve">It was on Saturday 16th June, 2018 at around 06:20 hrs at DG31 haulage front when the hauler vehicle BH02 plunged into the stationary push bikes in DG39. The incident happened when the hauler was coming out of the field packed with cane bundles to the mill. The vehicle was exiting DG31 through the tail-ditch side of the field and Feeder load side of DG39._x000D_
+    <t xml:space="preserve">"It was on Saturday 16th June, 2018 at around 06:20 hrs at DG31 haulage front when the hauler vehicle BH02 plunged into the stationary push bikes in DG39. The incident happened when the hauler was coming out of the field packed with cane bundles to the mill. The vehicle was exiting DG31 through the tail-ditch side of the field and Feeder load side of DG39._x000D_
  _x000D_
 After a thorough investigation, it was found out that the vehicle BH02 lost its trailers as it was coming out of the field (DG31) as the driver was crossing the ridges to negotiate a corner into the haulage road at DG31-39 fields._x000D_
 The driver was accelerating so that he should come out of the field and hence that’s when the vehicle (BH02) lost its trailers, from the force exerted from acceleration the vehicle horse crossed the road and the feeder of DG39 into the field where the haulage cane Gleaners kept their bicycles. The bicycles were crushed and got damaged beyond repair._x000D_
@@ -130,33 +125,36 @@
 No injuries occurred during the incident as the driver come out un-injured and there was no person near the bicycles at DG39._x000D_
 _x000D_
 _x000D_
+</t>
+  </si>
+  <si>
+    <t>[{'name': 'Verison Chunga', 'role': 'Gleaner at Haulage front', 'injury': 'No injury'}, {'name': 'Usher Lungu', 'role': 'Gleaner at Haulage front', 'injury': 'No injury'}, {'name': 'Putty Petros', 'role': 'Driver', 'injury': 'No injury'}]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The vehicle was coming out of the hauled field DG31 through the field tail-ditch and not the feeder as it supposed to do _x000D_
+_x000D_
+The vehicle lost its trailers and plunged into DG39 at the same time the cane haulage activity was put to hold_x000D_
 _x000D_
 </t>
   </si>
   <si>
-    <t>[{'name': 'Verison Chunga', 'role': 'Gleaner at Haulage front', 'injury': 'No injury'}, {'name': 'Usher Lungu', 'role': 'Gleaner at Haulage front', 'injury': 'No injury'}, {'name': 'Putty Petros', 'role': 'Driver', 'injury': 'No injury'}]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The vehicle was coming out of the hauled field DG31 through the field tail-ditch and not the feeder as it supposed to do _x000D_
-The vehicle lost its trailers and plunged into DG39 at the same time the cane haulage activity was put to hold_x000D_
+    <t xml:space="preserve">Poor road conditions at the tailditch _x000D_
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poor road conditions at the tailditch </t>
   </si>
   <si>
     <t xml:space="preserve">It was in the morning and the weather was clear and dry._x000D_
 _x000D_
-Driver tested negative for alcohol </t>
+Driver tested negative for alcohol_x000D_
+</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>[{'action': 'Lock nut to be installed on the hauler to hold the ball and socket connection', 'responsible': 'M. SICHINGA', 'due': '2018-06-16', 'status': 'Open'}]</t>
+    <t>No</t>
+  </si>
+  <si>
+    <t>[{'action': 'Lock nut to be installed on the hauler to hold the ball and socket connection', 'responsible': 'M. SICHINGA', 'due': '2018-06-16', 'status': 'Open'}, {'action': 'Assemble point to be clearly demarcated with red-tape for high visibility', 'responsible': 'P. SIBALE', 'due': '2018-06-16', 'status': 'In Progress'}, {'action': 'Assemble points to be developed behind the haulage main root', 'responsible': 'P. SIBALE', 'due': '2018-06-17', 'status': 'Open'}, {'action': 'All personal belongings to be kept at the assemble point at haulage front', 'responsible': 'P. SIBALE', 'due': '2018-06-16', 'status': 'Completed'}]</t>
   </si>
   <si>
     <t>Humphrey Lungu</t>
@@ -168,17 +166,17 @@
     <t>2018-06-18</t>
   </si>
   <si>
-    <t>74ff597804244c7ca09f2d3f8c785868_ffd94186cd244b269ab609c9fe03cc11_INCIDENT_DG39-1.jpg;74ff597804244c7ca09f2d3f8c785868_f6900683038d41e4a41ea42e2505e1c8_INCIDENT_DG39-2.jpg</t>
-  </si>
-  <si>
-    <t>2025-12-03T13:32:29.976988</t>
+    <t>ba90ac0c9fef442791e165f9ac4cfea0_b829d87590b5457dba4e1c6553f4f825_INCIDENT_DG39-1.jpg;ba90ac0c9fef442791e165f9ac4cfea0_35f98af0370e442ab49df528983cddeb_INCIDENT_DG39-2.jpg</t>
+  </si>
+  <si>
+    <t>2025-12-03T19:40:37.198396</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,14 +239,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -295,7 +285,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -327,10 +317,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -362,7 +351,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -538,14 +526,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:X2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -619,7 +604,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
         <v>24</v>
       </c>

--- a/data/incidents_full_report.xlsx
+++ b/data/incidents_full_report.xlsx
@@ -14,11 +14,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Report_Number</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
     <t>Incident_Date</t>
   </si>
   <si>
@@ -49,6 +55,12 @@
     <t>Affected_Persons</t>
   </si>
   <si>
+    <t>Affected_Persons_Details</t>
+  </si>
+  <si>
+    <t>Sequence_of_Events</t>
+  </si>
+  <si>
     <t>Contributing_Factors</t>
   </si>
   <si>
@@ -70,113 +82,128 @@
     <t>Corrective_Actions</t>
   </si>
   <si>
-    <t>Investigator</t>
-  </si>
-  <si>
-    <t>Investigation_Date</t>
-  </si>
-  <si>
-    <t>Prepared_By</t>
-  </si>
-  <si>
-    <t>Prepared_Date</t>
+    <t>Supervisor_Name</t>
+  </si>
+  <si>
+    <t>Supervisor_Date</t>
+  </si>
+  <si>
+    <t>HSO_Name</t>
+  </si>
+  <si>
+    <t>HSO_Date</t>
+  </si>
+  <si>
+    <t>Manager_Name</t>
+  </si>
+  <si>
+    <t>Manager_Date</t>
+  </si>
+  <si>
+    <t>Approvals</t>
   </si>
   <si>
     <t>Photos</t>
   </si>
   <si>
+    <t>QR_Path</t>
+  </si>
+  <si>
     <t>Created_At</t>
   </si>
   <si>
-    <t>ba90ac0c9fef442791e165f9ac4cfea0</t>
-  </si>
-  <si>
-    <t>2018-06-16</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>George Shonga</t>
-  </si>
-  <si>
-    <t>Agriculture, Cane cutting/ Haulage</t>
-  </si>
-  <si>
-    <t>Main Estate DG39000</t>
+    <t>Updated_At</t>
+  </si>
+  <si>
+    <t>015b815a034e428083bda0865e33c1c1</t>
+  </si>
+  <si>
+    <t>RPT-20251205-0001</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>Joseph Mseteka</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>DG13000</t>
   </si>
   <si>
     <t>Accident</t>
   </si>
   <si>
-    <t>Stopped the operation</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"It was on Saturday 16th June, 2018 at around 06:20 hrs at DG31 haulage front when the hauler vehicle BH02 plunged into the stationary push bikes in DG39. The incident happened when the hauler was coming out of the field packed with cane bundles to the mill. The vehicle was exiting DG31 through the tail-ditch side of the field and Feeder load side of DG39._x000D_
- _x000D_
-After a thorough investigation, it was found out that the vehicle BH02 lost its trailers as it was coming out of the field (DG31) as the driver was crossing the ridges to negotiate a corner into the haulage road at DG31-39 fields._x000D_
-The driver was accelerating so that he should come out of the field and hence that’s when the vehicle (BH02) lost its trailers, from the force exerted from acceleration the vehicle horse crossed the road and the feeder of DG39 into the field where the haulage cane Gleaners kept their bicycles. The bicycles were crushed and got damaged beyond repair._x000D_
-The vehicle was removed from DG39 and the push bikes were collected by CHL through the Haulage Supervisor on that time Mr. Stambuli, and the driver involved to this incident was Putty Petros driving BH02._x000D_
-The two (2) damaged bicycles belongs to Verison Chunga and Usher Lungu employees of DCGL as gleaners at cutting front._x000D_
-_x000D_
-No injuries occurred during the incident as the driver come out un-injured and there was no person near the bicycles at DG39._x000D_
-_x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>[{'name': 'Verison Chunga', 'role': 'Gleaner at Haulage front', 'injury': 'No injury'}, {'name': 'Usher Lungu', 'role': 'Gleaner at Haulage front', 'injury': 'No injury'}, {'name': 'Putty Petros', 'role': 'Driver', 'injury': 'No injury'}]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The vehicle was coming out of the hauled field DG31 through the field tail-ditch and not the feeder as it supposed to do _x000D_
-_x000D_
-The vehicle lost its trailers and plunged into DG39 at the same time the cane haulage activity was put to hold_x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poor road conditions at the tailditch _x000D_
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It was in the morning and the weather was clear and dry._x000D_
-_x000D_
-Driver tested negative for alcohol_x000D_
-</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>[{'action': 'Lock nut to be installed on the hauler to hold the ball and socket connection', 'responsible': 'M. SICHINGA', 'due': '2018-06-16', 'status': 'Open'}, {'action': 'Assemble point to be clearly demarcated with red-tape for high visibility', 'responsible': 'P. SIBALE', 'due': '2018-06-16', 'status': 'In Progress'}, {'action': 'Assemble points to be developed behind the haulage main root', 'responsible': 'P. SIBALE', 'due': '2018-06-17', 'status': 'Open'}, {'action': 'All personal belongings to be kept at the assemble point at haulage front', 'responsible': 'P. SIBALE', 'due': '2018-06-16', 'status': 'Completed'}]</t>
-  </si>
-  <si>
-    <t>Humphrey Lungu</t>
-  </si>
-  <si>
-    <t>PETER SIBALE</t>
-  </si>
-  <si>
-    <t>2018-06-18</t>
-  </si>
-  <si>
-    <t>ba90ac0c9fef442791e165f9ac4cfea0_b829d87590b5457dba4e1c6553f4f825_INCIDENT_DG39-1.jpg;ba90ac0c9fef442791e165f9ac4cfea0_35f98af0370e442ab49df528983cddeb_INCIDENT_DG39-2.jpg</t>
-  </si>
-  <si>
-    <t>2025-12-03T19:40:37.198396</t>
+    <t>Miss Regina Clement sustained an eye injury during feeder maintenance operation at DG13000. The injury come about by the cane ash that entered her right eye will working.</t>
+  </si>
+  <si>
+    <t>[{"name": "Regina Clement", "emp_id": "ES2086", "sex": "Female", "age": "25", "years_service": "2", "role": "General worker", "injury": "Eye injury"}]</t>
+  </si>
+  <si>
+    <t>[{"date": "2024-07-18", "time": "06:00", "details": "Miss Regina was assigned to do feeder maintenance at DG13000 "}, {"date": "2024-07-18", "time": "11:00", "details": "Cane ash entered into Miss Regina right eye, she continued working up to the end of her task"}, {"date": "2024-07-22", "time": "14:30", "details": "Mr. Chatayika the Capitao was passing through Miss Regina's house and noticed that she was in deep pain"}, {"date": "2024-07-22", "time": "14:31", "details": "Mr. Chatayika inquired of the problem and he was told that she got injured on 18 July at DG13000. The Capitao advised her to go to the clinic"}, {"date": "2024-07-22", "time": "14:45", "details": "Miss Regina was checked and treated with eye drops at DCGL clinic "}, {"date": "2024-07-27", "time": "14:00", "details": "The incident was reported to the Safety Officer and Agriculture management during the planning meeting. The meeting agreed that the Safety officer should make a follow-up on the injured person"}, {"date": "2024-07-27", "time": "15:30", "details": "The injured person was referred to Nkhotakota district hospital for further treatment "}, {"date": "2024-07-27", "time": "16:30", "details": "The doctors examined and further treated the injured eye. The doctors report show severe eye damage "}]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wind was relatively strong on this day _x000D_
+Cane ash </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cane ash </t>
+  </si>
+  <si>
+    <t>Working without protective gear (goggles)_x000D_
+Workers not following safety procedures (Applying 4 stapes to Safety and 4 Currencies)_x000D_
+The company has poor incident reporting procedure</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>[{"action": "Introduce safety culture at work place", "responsible": "Felix Lungu", "due": "2024-08-01", "status": "In Progress"}, {"action": "Management needs to review its PPE policy so that the purchasing and issuing of PPE is done on time and to every one", "responsible": "Felix Lungu", "due": "2024-08-01", "status": "Open"}, {"action": "Workers to be aware of the 4 Steps to Safety and 4 Currencies to Safety", "responsible": "Humphrey Lungu", "due": "2024-08-01", "status": "Open"}, {"action": "Introduce safety culture at work place", "responsible": "Felix Lungu", "due": "2024-08-01", "status": "In Progress"}]</t>
+  </si>
+  <si>
+    <t>Felix Lungu</t>
+  </si>
+  <si>
+    <t>2024-08-05</t>
+  </si>
+  <si>
+    <t>Allan Chengo</t>
+  </si>
+  <si>
+    <t>2024-08-07</t>
+  </si>
+  <si>
+    <t>Chanaga Banda</t>
+  </si>
+  <si>
+    <t>2024-08-08</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>015b815a034e428083bda0865e33c1c1_606ad8e0d26e447d882ec59ca90725e7_ps.png</t>
+  </si>
+  <si>
+    <t>https://chart.googleapis.com/chart?cht=qr&amp;chs=200x200&amp;chl=http%3A%2F%2F127.0.0.1%3A5000incident-report%2F015b815a034e428083bda0865e33c1c1&amp;chld=L|1</t>
+  </si>
+  <si>
+    <t>2025-12-05T12:34:52.787357</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,6 +218,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -225,16 +259,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -527,10 +567,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:33">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -603,82 +643,130 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:33">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
+        <v>34</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="O2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="Q2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="S2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="T2" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="U2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="X2" t="s">
-        <v>45</v>
+        <v>51</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="AE2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/incidents_full_report.xlsx
+++ b/data/incidents_full_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -82,6 +82,18 @@
     <t>Corrective_Actions</t>
   </si>
   <si>
+    <t>Investigator</t>
+  </si>
+  <si>
+    <t>Investigation_Date</t>
+  </si>
+  <si>
+    <t>Prepared_By</t>
+  </si>
+  <si>
+    <t>Prepared_Date</t>
+  </si>
+  <si>
     <t>Supervisor_Name</t>
   </si>
   <si>
@@ -115,88 +127,259 @@
     <t>Updated_At</t>
   </si>
   <si>
+    <t>Investigator.1</t>
+  </si>
+  <si>
+    <t>Investigation_Date.1</t>
+  </si>
+  <si>
+    <t>Prepared_By.1</t>
+  </si>
+  <si>
+    <t>Prepared_Date.1</t>
+  </si>
+  <si>
     <t>015b815a034e428083bda0865e33c1c1</t>
   </si>
   <si>
+    <t>1b404fb44e7f4f8f86f09080a7683026</t>
+  </si>
+  <si>
+    <t>3261aeeb69234107b118601f7313947c</t>
+  </si>
+  <si>
     <t>RPT-20251205-0001</t>
   </si>
   <si>
+    <t>RPT-20251208-0001</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>2024-07-18</t>
   </si>
   <si>
+    <t>2023-10-26</t>
+  </si>
+  <si>
+    <t>2025-12-08</t>
+  </si>
+  <si>
     <t>11:00</t>
   </si>
   <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
     <t>Joseph Mseteka</t>
   </si>
   <si>
+    <t>Hopeson Masiye</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
+    <t>Human Resources/ Security</t>
+  </si>
+  <si>
+    <t>Chawala Cane Cutting</t>
+  </si>
+  <si>
     <t>DG13000</t>
   </si>
   <si>
+    <t>Site 4</t>
+  </si>
+  <si>
+    <t>Ukasi</t>
+  </si>
+  <si>
     <t>Accident</t>
   </si>
   <si>
+    <t>Near Miss</t>
+  </si>
+  <si>
     <t>Miss Regina Clement sustained an eye injury during feeder maintenance operation at DG13000. The injury come about by the cane ash that entered her right eye will working.</t>
   </si>
   <si>
+    <t>Mr. Livingston Alumani working as a security officer was assigned to work at Site 4 compound. At around 9:40 am he climbed a mango tree to pluck some mangos to eat, the tree branch that supported him breaks due to his weight. He felled from the mango tree at an estimated height of four meters.   He fell facing down which sustained a chest injury that resulted into loosing conscious and internal bleeding</t>
+  </si>
+  <si>
+    <t>Kuyesa nawo</t>
+  </si>
+  <si>
     <t>[{"name": "Regina Clement", "emp_id": "ES2086", "sex": "Female", "age": "25", "years_service": "2", "role": "General worker", "injury": "Eye injury"}]</t>
   </si>
   <si>
+    <t>[{"name": "Livingstone Alumani", "emp_id": "D00334", "sex": "Male", "age": "36", "years_service": "5", "role": "Security Guard", "injury": "Internal bleeding"}]</t>
+  </si>
+  <si>
+    <t>[{"name": "Verison Chunga", "emp_id": "D00334", "sex": "Male", "age": "18", "years_service": "3", "role": "General worker", "injury": "No injury"}]</t>
+  </si>
+  <si>
     <t>[{"date": "2024-07-18", "time": "06:00", "details": "Miss Regina was assigned to do feeder maintenance at DG13000 "}, {"date": "2024-07-18", "time": "11:00", "details": "Cane ash entered into Miss Regina right eye, she continued working up to the end of her task"}, {"date": "2024-07-22", "time": "14:30", "details": "Mr. Chatayika the Capitao was passing through Miss Regina's house and noticed that she was in deep pain"}, {"date": "2024-07-22", "time": "14:31", "details": "Mr. Chatayika inquired of the problem and he was told that she got injured on 18 July at DG13000. The Capitao advised her to go to the clinic"}, {"date": "2024-07-22", "time": "14:45", "details": "Miss Regina was checked and treated with eye drops at DCGL clinic "}, {"date": "2024-07-27", "time": "14:00", "details": "The incident was reported to the Safety Officer and Agriculture management during the planning meeting. The meeting agreed that the Safety officer should make a follow-up on the injured person"}, {"date": "2024-07-27", "time": "15:30", "details": "The injured person was referred to Nkhotakota district hospital for further treatment "}, {"date": "2024-07-27", "time": "16:30", "details": "The doctors examined and further treated the injured eye. The doctors report show severe eye damage "}]</t>
   </si>
   <si>
-    <t xml:space="preserve">Wind was relatively strong on this day _x000D_
-Cane ash </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cane ash </t>
-  </si>
-  <si>
-    <t>Working without protective gear (goggles)_x000D_
-Workers not following safety procedures (Applying 4 stapes to Safety and 4 Currencies)_x000D_
+    <t>[{"date": "2023-10-26", "time": "06:00", "details": "Mr. Livingston Alumani was assigned to guard at Site 4 compound"}, {"date": "2023-10-26", "time": "06:15", "details": "He reached the working post and did the shift hand overs with the night guard"}, {"date": "2023-10-26", "time": "09:40", "details": "Mr. Alumani saw some mangos in the tree at Miss Nuka's house, closer to Mr. H. Masiye's house. He made a decision to climb and pluck the mangos to eat while on post"}, {"date": "2023-10-26", "time": "09:45", "details": "Mr. Alumani reached the high branches where the mangos were, He managed to pluck a few and kept them in his uniform trouser pockets. Unfortunately the tree blanch breaks. Mr. Alumani fall from the tree to the ground.  "}, {"date": "2023-10-26", "time": "09:45", "details": "Mr. H Masiye held something has fallen down from the mango tree and was big. He went to check what it was. Upon reaching the place he saw a fallen mango branch and a security guard in uniform laying on the ground and not moving"}, {"date": "2023-10-26", "time": "09:54", "details": "Mr. Masiye carried the unconscious guard to DCGL clinic. The clinic team gave the injured person a drip of water and referred him to Matiki clinic "}, {"date": "2023-10-26", "time": "10:09", "details": "Doctors worked on Mr. Alumani trying to drain the internal bleeding and then referred him to Nkhotakota district hospital for further treatment "}]</t>
+  </si>
+  <si>
+    <t>[{"date": "2025-12-08", "time": "06:30", "details": "Kuyesa yesa"}]</t>
+  </si>
+  <si>
+    <t>Wind was relatively strong on this day_x005F_x000D__x005F_x000D__x005F_x000D__x005F_x000D__x005F_x000D_
+Cane ash</t>
+  </si>
+  <si>
+    <t>_x005F_x000D_</t>
+  </si>
+  <si>
+    <t>_x005F_x000D__x000D_
+            Kuyesa chabe</t>
+  </si>
+  <si>
+    <t>Cane ash</t>
+  </si>
+  <si>
+    <t>Falling from a mango tree _x005F_x000D__x005F_x000D__x005F_x000D_
+_x005F_x000D_</t>
+  </si>
+  <si>
+    <t>_x005F_x000D__x000D_
+            Nanu zomwezi mpaka apa</t>
+  </si>
+  <si>
+    <t>Working without protective gear (goggles)_x005F_x000D__x005F_x000D__x005F_x000D__x005F_x000D__x005F_x000D_
+Workers not following safety procedures (Applying 4 stapes to Safety and 4 Currencies)_x005F_x000D__x005F_x000D__x005F_x000D__x005F_x000D__x005F_x000D_
 The company has poor incident reporting procedure</t>
   </si>
   <si>
+    <t>The victim fall from a height of about four meters from a mango tree _x005F_x000D_
+He climbed the tree with his security boots on_x005F_x000D_
+He was severe injured and unconscious when found (picture 2). Note that this picture is a simulation of the event and not the real victim_x005F_x000D_
+He was on duty as his working tools (Button stick and Barret) were carefully kept on a hip of bricks meant for fence maintenance _x005F_x000D_
+He was unable to talk and he was bleeding from the mouth and nose_x005F_x000D_
+He wore his PPE at the time of the incident (security uniform), this was evident as foot prints around the mango tree were visible (picture 1)</t>
+  </si>
+  <si>
+    <t>_x005F_x000D__x000D_
+            Zikugwira kapena ayi</t>
+  </si>
+  <si>
     <t>High</t>
   </si>
   <si>
+    <t>Low</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>[{"action": "Introduce safety culture at work place", "responsible": "Felix Lungu", "due": "2024-08-01", "status": "In Progress"}, {"action": "Management needs to review its PPE policy so that the purchasing and issuing of PPE is done on time and to every one", "responsible": "Felix Lungu", "due": "2024-08-01", "status": "Open"}, {"action": "Workers to be aware of the 4 Steps to Safety and 4 Currencies to Safety", "responsible": "Humphrey Lungu", "due": "2024-08-01", "status": "Open"}, {"action": "Introduce safety culture at work place", "responsible": "Felix Lungu", "due": "2024-08-01", "status": "In Progress"}]</t>
+    <t>No</t>
+  </si>
+  <si>
+    <t>[{"action": "Workers to be aware of the 4 Steps to Safety and 4 Currencies to Safety", "responsible": "Humphrey Lungu", "due": "2024-08-01", "status": "In Progress"}, {"action": "Management needs to review its PPE policy so that the purchasing and issuing of PPE is done on time and to every one", "responsible": "Felix Lungu", "due": "2024-08-01", "status": "Open"}, {"action": "Introduce safety culture at work place", "responsible": "Felix Lungu", "due": "2024-08-01", "status": "Open"}]</t>
+  </si>
+  <si>
+    <t>[{"action": "Introduced the culture of Take 5 meetings at work place", "responsible": "SHERQ office", "due": "2023-11-01", "status": "Open"}, {"action": "Employees and other people living at DCGL to be aligned on Safety awareness", "responsible": "SHERQ office and HR office", "due": "2023-12-30", "status": "Open"}, {"action": "Management banned climbing of trees at every house hold", "responsible": "HR office", "due": "2023-10-26", "status": "Completed"}]</t>
+  </si>
+  <si>
+    <t>[{"action": "try again", "responsible": "Felix Lungu", "due": "2025-12-10", "status": "Open"}]</t>
+  </si>
+  <si>
+    <t>Goerge Shonga, Thokozani Mlauzi, Humphrey Lungu</t>
+  </si>
+  <si>
+    <t>Humphrey Lungu</t>
+  </si>
+  <si>
+    <t>2024-07-27</t>
+  </si>
+  <si>
+    <t>PETER SIBALE</t>
+  </si>
+  <si>
+    <t>2024-07-31</t>
+  </si>
+  <si>
+    <t>2023-10-30</t>
   </si>
   <si>
     <t>Felix Lungu</t>
   </si>
   <si>
+    <t>Edward Kaziputa</t>
+  </si>
+  <si>
     <t>2024-08-05</t>
   </si>
   <si>
+    <t>2023-11-03</t>
+  </si>
+  <si>
     <t>Allan Chengo</t>
   </si>
   <si>
     <t>2024-08-07</t>
   </si>
   <si>
+    <t>2023-11-04</t>
+  </si>
+  <si>
     <t>Chanaga Banda</t>
   </si>
   <si>
     <t>2024-08-08</t>
   </si>
   <si>
+    <t>2023-11-05</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
-    <t>015b815a034e428083bda0865e33c1c1_606ad8e0d26e447d882ec59ca90725e7_ps.png</t>
+    <t>015b815a034e428083bda0865e33c1c1_606ad8e0d26e447d882ec59ca90725e7_ps.png;015b815a034e428083bda0865e33c1c1_98c46bf85a0944189e59fdf1c5a6cbf3_logo.png;015b815a034e428083bda0865e33c1c1_86320b0b14e642ed9f9572f8c26719b3_arashiyama-bamboo-grove-kyoto-e1466611768221.jpg</t>
+  </si>
+  <si>
+    <t>1b404fb44e7f4f8f86f09080a7683026_530865af6db84f1dab373a8cf0f12701_INCIDENT_DG39-2.jpg;1b404fb44e7f4f8f86f09080a7683026_cc2862c1543a42f587674e2aa7fe58b8_Screenshot_42.png</t>
+  </si>
+  <si>
+    <t>3261aeeb69234107b118601f7313947c_d51876c2a56445038af2a90b6ab51482_Screenshot_5.png</t>
   </si>
   <si>
     <t>https://chart.googleapis.com/chart?cht=qr&amp;chs=200x200&amp;chl=http%3A%2F%2F127.0.0.1%3A5000incident-report%2F015b815a034e428083bda0865e33c1c1&amp;chld=L|1</t>
   </si>
   <si>
+    <t>https://chart.googleapis.com/chart?cht=qr&amp;chs=200x200&amp;chl=http%3A%2F%2F127.0.0.1%3A5000incident-report%2F1b404fb44e7f4f8f86f09080a7683026&amp;chld=L|1</t>
+  </si>
+  <si>
+    <t>https://chart.googleapis.com/chart?cht=qr&amp;chs=200x200&amp;chl=http%3A%2F%2F127.0.0.1%3A5000%2Fincident-report%2F3261aeeb69234107b118601f7313947c&amp;chld=L|1</t>
+  </si>
+  <si>
     <t>2025-12-05T12:34:52.787357</t>
+  </si>
+  <si>
+    <t>2025-12-05T23:14:24.038380</t>
+  </si>
+  <si>
+    <t>2025-12-08T12:33:52.669155</t>
+  </si>
+  <si>
+    <t>2025-12-05T21:54:59.344612</t>
+  </si>
+  <si>
+    <t>2025-12-08T11:55:24.326329</t>
+  </si>
+  <si>
+    <t>2025-12-08T12:45:14.262876</t>
   </si>
 </sst>
 </file>
@@ -567,10 +750,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AO4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:41">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -670,102 +853,330 @@
       <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="I2" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="N2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>76</v>
+      </c>
+      <c r="R2" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" t="s">
+        <v>82</v>
+      </c>
+      <c r="T2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U2" t="s">
+        <v>84</v>
+      </c>
+      <c r="V2" t="s">
+        <v>86</v>
+      </c>
+      <c r="W2" t="s">
+        <v>89</v>
+      </c>
+      <c r="X2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41">
+      <c r="A3" t="s">
         <v>42</v>
       </c>
-      <c r="O2" t="s">
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" t="s">
+        <v>62</v>
+      </c>
+      <c r="L3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N3" t="s">
+        <v>68</v>
+      </c>
+      <c r="O3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P3" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>77</v>
+      </c>
+      <c r="R3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S3" t="s">
+        <v>82</v>
+      </c>
+      <c r="T3" t="s">
+        <v>84</v>
+      </c>
+      <c r="U3" t="s">
+        <v>84</v>
+      </c>
+      <c r="V3" t="s">
+        <v>87</v>
+      </c>
+      <c r="W3" t="s">
+        <v>90</v>
+      </c>
+      <c r="X3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41">
+      <c r="A4" t="s">
         <v>43</v>
       </c>
-      <c r="P2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="B4" t="s">
         <v>45</v>
       </c>
-      <c r="R2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S2" t="s">
-        <v>47</v>
-      </c>
-      <c r="T2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V2" t="s">
-        <v>49</v>
-      </c>
-      <c r="W2" t="s">
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
         <v>50</v>
       </c>
-      <c r="X2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="E4" t="s">
         <v>53</v>
       </c>
-      <c r="AA2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="F4" t="s">
         <v>55</v>
       </c>
-      <c r="AC2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE2" s="2" t="s">
+      <c r="G4" t="s">
         <v>58</v>
       </c>
-      <c r="AF2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>59</v>
+      <c r="H4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L4" t="s">
+        <v>66</v>
+      </c>
+      <c r="N4" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" t="s">
+        <v>72</v>
+      </c>
+      <c r="P4" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R4" t="s">
+        <v>81</v>
+      </c>
+      <c r="S4" t="s">
+        <v>83</v>
+      </c>
+      <c r="T4" t="s">
+        <v>85</v>
+      </c>
+      <c r="U4" t="s">
+        <v>85</v>
+      </c>
+      <c r="V4" t="s">
+        <v>88</v>
+      </c>
+      <c r="W4" t="s">
+        <v>90</v>
+      </c>
+      <c r="X4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AE2" r:id="rId1"/>
+    <hyperlink ref="AI2" r:id="rId1"/>
+    <hyperlink ref="AI3" r:id="rId2"/>
+    <hyperlink ref="AI4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
